--- a/Outcome/Appendix/Tables/Seasonal_shift_uncertainty.xlsx
+++ b/Outcome/Appendix/Tables/Seasonal_shift_uncertainty.xlsx
@@ -2151,10 +2151,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
